--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -702,16 +702,16 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>2.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.39</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>3.68</v>
       </c>
       <c r="N3" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -831,16 +831,16 @@
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.39</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>3.68</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>6.08</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.55</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>2.85</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,34 +936,34 @@
         <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y4" t="n">
         <v>2.05</v>
@@ -972,16 +972,16 @@
         <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>3.28</v>
       </c>
       <c r="O2" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.08</v>
+        <v>3.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="U2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.33</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH2" t="n">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.39</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="N3" t="n">
-        <v>2.85</v>
+        <v>4.8</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>6.08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="O4" t="n">
         <v>2.12</v>
@@ -966,10 +966,10 @@
         <v>2.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AA4" t="n">
         <v>3.58</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N2" t="n">
-        <v>3.28</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.16</v>
+        <v>6.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.8</v>
+        <v>3.28</v>
       </c>
       <c r="O3" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.08</v>
+        <v>3.16</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="U3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
         <v>1.33</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH3" t="n">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.62</v>
+        <v>2.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.08</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="U2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.33</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH2" t="n">
-        <v>2.21</v>
+        <v>1.38</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.2</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>3.68</v>
       </c>
       <c r="N3" t="n">
-        <v>3.28</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.16</v>
+        <v>5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.05</v>
+        <v>3.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>2.21</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>3.78</v>
+        <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>2.12</v>
@@ -945,16 +945,16 @@
         <v>6.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S4" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -966,10 +966,10 @@
         <v>2.92</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AA4" t="n">
         <v>3.58</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.39</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>3.68</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="Q2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T2" t="n">
         <v>3</v>
       </c>
-      <c r="R2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>3.16</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.19</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.05</v>
+        <v>3.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,77 +798,77 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>2.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.38</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>2.21</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -936,13 +936,13 @@
         <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="P4" t="n">
         <v>2.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.3</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>1.4</v>
@@ -957,7 +957,7 @@
         <v>1.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
         <v>1.31</v>
@@ -975,7 +975,7 @@
         <v>3.58</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AC4" t="n">
         <v>2.1</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,77 +669,77 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>2.2</v>
       </c>
       <c r="M2" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>3.28</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>3.54</v>
       </c>
       <c r="P2" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="Q2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.33</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X2" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AH2" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.39</v>
+        <v>1.66</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="N3" t="n">
-        <v>2.85</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="Q3" t="n">
+        <v>5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T3" t="n">
         <v>3</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>3.16</v>
-      </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.16</v>
+        <v>3.72</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="P4" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="Q4" t="n">
         <v>6</v>
       </c>
       <c r="R4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W4" t="n">
         <v>1.4</v>
       </c>
-      <c r="S4" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.31</v>
-      </c>
       <c r="X4" t="n">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Z4" t="n">
         <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.23</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>3.28</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
         <v>3.54</v>
@@ -702,16 +702,16 @@
         <v>1.03</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
         <v>4.1</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.66</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
         <v>2.2</v>
@@ -837,10 +837,10 @@
         <v>2.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA3" t="n">
         <v>3.72</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>2.06</v>
@@ -966,7 +966,7 @@
         <v>2.89</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
         <v>1.68</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.39</v>
+        <v>1.62</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>3.7</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>5.76</v>
       </c>
       <c r="O2" t="n">
-        <v>3.54</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>5.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.22</v>
+        <v>2.99</v>
       </c>
       <c r="U2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.1</v>
+        <v>3.72</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45944.8125</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>2.78</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>2.52</v>
       </c>
       <c r="O3" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>2.23</v>
+        <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="X3" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.18</v>
+        <v>1.4</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45944.8125</v>
@@ -927,61 +927,61 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="M4" t="n">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="N4" t="n">
-        <v>5.6</v>
+        <v>6.03</v>
       </c>
       <c r="O4" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="P4" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>6.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="T4" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="U4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X4" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.72</v>
+        <v>4.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,16 +994,16 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45944.89583333334</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="N2" t="n">
-        <v>5.76</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
         <v>2.2</v>
@@ -708,10 +708,10 @@
         <v>2.88</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="n">
         <v>3.72</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.78</v>
+        <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="O3" t="n">
         <v>3.5</v>
@@ -831,16 +831,16 @@
         <v>1.04</v>
       </c>
       <c r="W3" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
         <v>2.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
         <v>4.05</v>
@@ -927,13 +927,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
-        <v>3.54</v>
+        <v>3.59</v>
       </c>
       <c r="N4" t="n">
-        <v>6.03</v>
+        <v>5.6</v>
       </c>
       <c r="O4" t="n">
         <v>2.19</v>
@@ -966,10 +966,10 @@
         <v>2.7</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="AA4" t="n">
         <v>4.05</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -678,13 +678,13 @@
         <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="P2" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.98</v>
+        <v>5.25</v>
       </c>
       <c r="R2" t="n">
         <v>1.42</v>
@@ -723,7 +723,7 @@
         <v>2.06</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -807,28 +807,28 @@
         <v>2.85</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="P3" t="n">
         <v>1.92</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.28</v>
+        <v>2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
         <v>1.5</v>
@@ -843,16 +843,16 @@
         <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.05</v>
+        <v>4.21</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AI3" t="n">
         <v>2.1</v>
@@ -936,34 +936,34 @@
         <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.42</v>
+        <v>5.13</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
       </c>
       <c r="S4" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="T4" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="V4" t="n">
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="Y4" t="n">
         <v>2.05</v>
@@ -972,16 +972,16 @@
         <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.05</v>
+        <v>4.31</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="AI4" t="n">
         <v>1.5</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,61 +669,61 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="M2" t="n">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>5.6</v>
+        <v>2.85</v>
       </c>
       <c r="O2" t="n">
-        <v>2.18</v>
+        <v>3.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>5.25</v>
+        <v>3.07</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
         <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="X2" t="n">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.72</v>
+        <v>4.25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.89</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45944.8125</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.39</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>3.68</v>
       </c>
       <c r="N3" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="O3" t="n">
-        <v>3.26</v>
+        <v>2.19</v>
       </c>
       <c r="P3" t="n">
-        <v>1.92</v>
+        <v>2.09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.9</v>
+        <v>6.09</v>
       </c>
       <c r="R3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X3" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="Y3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH3" t="n">
         <v>2.19</v>
       </c>
-      <c r="Z3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AI3" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45944.8125</v>
@@ -936,13 +936,13 @@
         <v>5.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="P4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.13</v>
+        <v>5.32</v>
       </c>
       <c r="R4" t="n">
         <v>1.44</v>
@@ -963,7 +963,7 @@
         <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="Y4" t="n">
         <v>2.05</v>
@@ -972,16 +972,16 @@
         <v>1.68</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.31</v>
+        <v>4.37</v>
       </c>
       <c r="AB4" t="n">
         <v>1.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>1.29</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="AI4" t="n">
         <v>1.5</v>

--- a/jogos_2025-10-14.xlsx
+++ b/jogos_2025-10-14.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Paysandu</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.39</v>
+        <v>1.49</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>3.68</v>
       </c>
       <c r="N2" t="n">
-        <v>2.85</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.24</v>
+        <v>2.19</v>
       </c>
       <c r="P2" t="n">
-        <v>1.94</v>
+        <v>2.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.07</v>
+        <v>6.09</v>
       </c>
       <c r="R2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
         <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="W2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="X2" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="Y2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH2" t="n">
         <v>2.19</v>
       </c>
-      <c r="Z2" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.46</v>
-      </c>
       <c r="AI2" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2</v>
+        <v>2.87</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45944.8125</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Paysandu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -798,61 +798,61 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>2.39</v>
       </c>
       <c r="M3" t="n">
-        <v>3.68</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>5.6</v>
+        <v>2.85</v>
       </c>
       <c r="O3" t="n">
-        <v>2.19</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.09</v>
+        <v>3.07</v>
       </c>
       <c r="R3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
         <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V3" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W3" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2.83</v>
+        <v>2.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.02</v>
+        <v>2.19</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.76</v>
+        <v>4.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.68</v>
+        <v>1.89</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
@@ -865,16 +865,16 @@
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.19</v>
+        <v>1.46</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.87</v>
+        <v>2</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45944.8125</v>
